--- a/diagnostics_code/procedures.xlsx
+++ b/diagnostics_code/procedures.xlsx
@@ -2105,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2237,11 +2237,11 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>4020653</v>
+        <v>4006788</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fluoroscopy guided percutaneous transluminal balloon angioplasty of bypass graft of coronary artery with contrast</t>
+          <t>Percutaneous transluminal coronary angioplasty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>non-standard</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>4106556</v>
+        <v>4020074</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Coronary atherectomy by laser</t>
+          <t>Revascularization of wall of heart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2287,11 +2287,11 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>4150819</v>
+        <v>4020653</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operative procedure on coronary artery</t>
+          <t>Fluoroscopy guided percutaneous transluminal balloon angioplasty of bypass graft of coronary artery with contrast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2312,11 +2312,11 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>4172515</v>
+        <v>4050590</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Therapeutic procedure</t>
+          <t>Removal of coronary artery obstruction, percutaneous transluminal, multiple vessels</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2337,11 +2337,11 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>4181025</v>
+        <v>4051012</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fluoroscopy guided percutaneous transluminal balloon angioplasty with insertion of stent into coronary artery using fluoroscopic guidance with contrast</t>
+          <t>Angioplasty of arterial graft</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>non-standard</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>4184832</v>
+        <v>4051039</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal angioplasty of coronary artery using imaging guidance with contrast</t>
+          <t>Insertion of arterial stent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2387,11 +2387,11 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>4212973</v>
+        <v>4106556</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emergency percutaneous coronary intervention</t>
+          <t>Coronary atherectomy by laser</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2412,11 +2412,11 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>4216130</v>
+        <v>4139362</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Percutaneous coronary intervention</t>
+          <t>Percutaneous transluminal balloon angioplasty of artery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>non-standard</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>4225903</v>
+        <v>4150819</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fluoroscopy guided percutaneous transluminal angioplasty of coronary artery, multiple vessels with contrast</t>
+          <t>Operative procedure on coronary artery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2462,11 +2462,11 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>4287108</v>
+        <v>4167564</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Removal of coronary artery obstruction by percutaneous transluminal balloon, single vessel</t>
+          <t>Fluoroscopy guided angioplasty of artery with contrast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>non-standard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>37153378</v>
+        <v>4170285</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Percutaneous coronary intervention of intermediate artery of left main coronary artery</t>
+          <t>Myocardial revascularization</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2512,11 +2512,11 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>37153385</v>
+        <v>4171077</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Percutaneous coronary intervention on ostial left main coronary artery</t>
+          <t>Fluoroscopic angiography of coronary artery with contrast and insertion of stent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2537,11 +2537,11 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>37153597</v>
+        <v>4172515</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal insertion of bare metal stent into coronary artery using fluoroscopic guidance with contrast</t>
+          <t>Therapeutic procedure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2562,11 +2562,11 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>37154069</v>
+        <v>4178148</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Percutaneous coronary intervention on mid-segment of left main coronary artery</t>
+          <t>Placement of stent in anterior descending branch of left coronary artery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2587,11 +2587,11 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>37157437</v>
+        <v>4181025</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal angioplasty with insertion of drug-eluting stent into left main artery coronary artery using fluoroscopic guidance with contrast</t>
+          <t>Fluoroscopy guided percutaneous transluminal balloon angioplasty with insertion of stent into coronary artery using fluoroscopic guidance with contrast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2612,11 +2612,11 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>37157438</v>
+        <v>4181955</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fluoroscopy guided percutaneous transluminal balloon angioplasty of left main coronary artery with contrast</t>
+          <t>Endovascular insertion of stent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2637,11 +2637,11 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>37158379</v>
+        <v>4184298</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Percutaneous coronary intervention on distal segment of left main coronary artery</t>
+          <t>Fluoroscopy guided percutaneous transluminal angioplasty with contrast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2662,11 +2662,11 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>43531439</v>
+        <v>4184832</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fluoroscopy guided percutaneous insertion of drug eluting stent into coronary artery with contrast</t>
+          <t>Percutaneous transluminal angioplasty of coronary artery using imaging guidance with contrast</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2687,11 +2687,11 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>43531440</v>
+        <v>4197882</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal insertion of metal stent into coronary artery using fluoroscopic guidance with contrast</t>
+          <t>Fluoroscopic angiography of graft using contrast with insertion of stent</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2712,11 +2712,11 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>44511133</v>
+        <v>4207625</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other specified transluminal balloon angioplasty of coronary artery</t>
+          <t>Percutaneous transluminal angioplasty of vascular graft</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2737,11 +2737,11 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>44511138</v>
+        <v>4212973</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal atherectomy of coronary artery</t>
+          <t>Emergency percutaneous coronary intervention</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2762,11 +2762,11 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>44511139</v>
+        <v>4216130</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Other specified other therapeutic transluminal operations on coronary artery</t>
+          <t>Percutaneous coronary intervention</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2787,11 +2787,11 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>44511268</v>
+        <v>4216356</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal balloon angioplasty and insertion of 1-2 drug-eluting stents into coronary artery</t>
+          <t>Infusion of intra-arterial thrombolytic agent with percutaneous transluminal coronary angioplasty, multiple vessels</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2812,11 +2812,11 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>44511269</v>
+        <v>4217445</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal balloon angioplasty and insertion of 3 or more drug-eluting stents into coronary artery</t>
+          <t>Heart revascularization</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2837,11 +2837,11 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>44511270</v>
+        <v>4225903</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal balloon angioplasty and insertion of 1-2 stents into coronary artery</t>
+          <t>Fluoroscopy guided percutaneous transluminal angioplasty of coronary artery, multiple vessels with contrast</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2862,11 +2862,11 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>44511271</v>
+        <v>4238755</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Percutaneous transluminal balloon angioplasty and insertion of 3 or more stents into coronary artery NEC</t>
+          <t>Infusion of intra-arterial thrombolytic agent with percutaneous transluminal coronary angioplasty, single vessel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2887,11 +2887,11 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>44511272</v>
+        <v>4244719</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other specified percutaneous transluminal balloon angioplasty and insertion of stent into coronary artery</t>
+          <t>Removal of coronary artery obstruction by percutaneous transluminal balloon with thrombolytic agent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OPCS4</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2912,24 +2912,1024 @@
     </row>
     <row r="33">
       <c r="A33">
+        <v>4264285</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal coronary angioplasty by rotablation using imaging guidance with contrast</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>4264286</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Percutaneous rotational coronary endarterectomy</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>4265293</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal coronary angioplasty by rotablation, single vessel using imaging guidance with contrast</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>4283892</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Placement of stent in coronary artery</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>4286646</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal balloon angioplasty using imaging guidance with contrast</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>4287108</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Removal of coronary artery obstruction by percutaneous transluminal balloon, single vessel</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>4303797</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided angioplasty of coronary artery with contrast</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>non-standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>4328103</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Infusion of intra-arterial thrombolytic agent with percutaneous transluminal coronary angioplasty</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>4329263</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Placement of stent in circumflex branch of left coronary artery</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>4330920</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous transluminal angioplasty of coronary artery with contrast</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>4336469</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Percutaneous high speed rotational coronary atherectomy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>4337739</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Percutaneous directional coronary atherectomy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>4337740</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Percutaneous low speed rotational coronary atherectomy</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>35607959</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous transluminal angioplasty of coronary artery with contrast using drug eluting balloon catheter</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>37017357</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous transluminal revascularization of chronic total occlusion of coronary artery with contrast</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>37111313</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Placement of stent in coronary artery bypass graft</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>37153378</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Percutaneous coronary intervention of intermediate artery of left main coronary artery</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>37153385</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Percutaneous coronary intervention on ostial left main coronary artery</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>37153597</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal insertion of bare metal stent into coronary artery using fluoroscopic guidance with contrast</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>37154069</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Percutaneous coronary intervention on mid-segment of left main coronary artery</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>37157437</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal angioplasty with insertion of drug-eluting stent into left main artery coronary artery using fluoroscopic guidance with contrast</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>37157438</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous transluminal balloon angioplasty of left main coronary artery with contrast</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>37158379</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Percutaneous coronary intervention on distal segment of left main coronary artery</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>42537597</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous insertion of bioresorbable stent into coronary artery</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>42538258</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Endovascular insertion of drug eluting stent</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>42538259</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Endovascular insertion of drug coated stent</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>43531439</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous insertion of drug eluting stent into coronary artery with contrast</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>43531440</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal insertion of metal stent into coronary artery using fluoroscopic guidance with contrast</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>44511133</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Other specified transluminal balloon angioplasty of coronary artery</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>44511138</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal atherectomy of coronary artery</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>44511139</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Other specified other therapeutic transluminal operations on coronary artery</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>44511268</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal balloon angioplasty and insertion of 1-2 drug-eluting stents into coronary artery</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>44511269</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal balloon angioplasty and insertion of 3 or more drug-eluting stents into coronary artery</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>44511270</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal balloon angioplasty and insertion of 1-2 stents into coronary artery</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>44511271</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal balloon angioplasty and insertion of 3 or more stents into coronary artery NEC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>44511272</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Other specified percutaneous transluminal balloon angioplasty and insertion of stent into coronary artery</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OPCS4</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>44789455</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Insertion of drug-eluting coronary artery stent</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>44811692</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided primary percutaneous coronary intervention</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
         <v>45769224</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Fluoroscopy guided percutaneous transluminal cutting balloon angioplasty of coronary artery with contrast</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Procedure</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>45770795</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Percutaneous transluminal balloon angioplasty and insertion of drug eluting stent into coronary artery</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>46271002</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Fluoroscopy guided percutaneous transluminal arterial angioplasty with insertion of stent with contrast</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
